--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00934-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00934-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1D173402-8902-461B-9796-E6C39E676414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{60476D76-318F-4F7C-AE67-E3B364A2C8C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{4EFA2A2E-061F-4727-9F5C-034AE0FD38CD}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{9014AF53-0204-4CB7-BCDE-82440C92BDB6}"/>
   </bookViews>
   <sheets>
     <sheet name="00934-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1585,24 +1585,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F55BB3B-0F63-4F15-AFDF-45B566C0B39E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADCF49B7-EBE0-46FE-A242-AF4756F575FB}">
   <dimension ref="A1:R29"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.5546875" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="11.375" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="6" width="10.375" customWidth="1"/>
+    <col min="7" max="9" width="9.875" customWidth="1"/>
+    <col min="10" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="11.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1630,7 +1631,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1660,7 +1661,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1706,7 +1707,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1756,7 +1757,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1810,7 +1811,7 @@
         <v>7.25</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1836,7 +1837,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>26</v>
       </c>
@@ -1892,7 +1893,7 @@
         <v>0.62</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>26</v>
       </c>
@@ -1948,7 +1949,7 @@
         <v>0.59</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="49">
         <v>2025</v>
       </c>
@@ -2002,7 +2003,7 @@
         <v>3.89</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>26</v>
       </c>
@@ -2058,7 +2059,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>26</v>
       </c>
@@ -2114,7 +2115,7 @@
         <v>0.63</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>26</v>
       </c>
@@ -2170,7 +2171,7 @@
         <v>0.48</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
         <v>26</v>
       </c>
@@ -2226,7 +2227,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
         <v>26</v>
       </c>
@@ -2282,7 +2283,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>26</v>
       </c>
@@ -2338,7 +2339,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>26</v>
       </c>
@@ -2394,7 +2395,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
         <v>26</v>
       </c>
@@ -2450,7 +2451,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
         <v>26</v>
       </c>
@@ -2506,7 +2507,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>26</v>
       </c>
@@ -2562,7 +2563,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>26</v>
       </c>
@@ -2618,7 +2619,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>26</v>
       </c>
@@ -2674,7 +2675,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="51">
         <v>2024</v>
       </c>
@@ -2728,7 +2729,7 @@
         <v>4.5199999999999996</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>26</v>
       </c>
@@ -2784,7 +2785,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>26</v>
       </c>
@@ -2840,7 +2841,7 @@
         <v>0.63</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>26</v>
       </c>
@@ -2896,7 +2897,7 @@
         <v>0.72</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>26</v>
       </c>
@@ -2952,7 +2953,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>26</v>
       </c>
@@ -3008,7 +3009,7 @@
         <v>0.72</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>26</v>
       </c>
@@ -3064,7 +3065,7 @@
         <v>1.59</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="49" t="s">
         <v>66</v>
       </c>
